--- a/source_data/workbooks/Source_Data_ED_Fig9.xlsx
+++ b/source_data/workbooks/Source_Data_ED_Fig9.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="59">
   <si>
     <t>figure_panel</t>
   </si>
@@ -137,6 +137,9 @@
     <t>uncertainty_method</t>
   </si>
   <si>
+    <t>system_description</t>
+  </si>
+  <si>
     <t>Extended Data 9b</t>
   </si>
   <si>
@@ -149,6 +152,39 @@
     <t>SEA-AD held-out</t>
   </si>
   <si>
+    <t>Reactive fraction</t>
+  </si>
+  <si>
+    <t>Reactive/astrogl. ratio 35µm</t>
+  </si>
+  <si>
+    <t>Peripyramidal react. 35µm</t>
+  </si>
+  <si>
+    <t>partial_pearson_r</t>
+  </si>
+  <si>
+    <t>donors</t>
+  </si>
+  <si>
+    <t>all</t>
+  </si>
+  <si>
+    <t>&gt;=5y</t>
+  </si>
+  <si>
+    <t>&gt;=7y</t>
+  </si>
+  <si>
+    <t>held-out reference</t>
+  </si>
+  <si>
+    <t>NeuroFM</t>
+  </si>
+  <si>
+    <t>No error bars plotted</t>
+  </si>
+  <si>
     <t>Bulk reactive-astrocyte fraction</t>
   </si>
   <si>
@@ -156,30 +192,6 @@
   </si>
   <si>
     <t>Peripyramidal astrocyte-lineage reactivity, 35 um</t>
-  </si>
-  <si>
-    <t>partial_pearson_r</t>
-  </si>
-  <si>
-    <t>donors</t>
-  </si>
-  <si>
-    <t>all</t>
-  </si>
-  <si>
-    <t>&gt;=5y</t>
-  </si>
-  <si>
-    <t>&gt;=7y</t>
-  </si>
-  <si>
-    <t>held-out reference</t>
-  </si>
-  <si>
-    <t>NeuroFM</t>
-  </si>
-  <si>
-    <t>No error bars plotted</t>
   </si>
 </sst>
 </file>
@@ -722,14 +734,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:W13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="18.7109375" customWidth="1"/>
     <col min="3" max="3" width="39.7109375" customWidth="1"/>
     <col min="4" max="4" width="17.7109375" customWidth="1"/>
-    <col min="5" max="5" width="55.7109375" customWidth="1"/>
+    <col min="5" max="5" width="30.7109375" customWidth="1"/>
     <col min="6" max="6" width="19.7109375" customWidth="1"/>
     <col min="7" max="7" width="13.7109375" customWidth="1"/>
     <col min="8" max="8" width="10.7109375" customWidth="1"/>
@@ -744,9 +756,10 @@
     <col min="20" max="20" width="20.7109375" customWidth="1"/>
     <col min="21" max="21" width="19.7109375" customWidth="1"/>
     <col min="22" max="22" width="23.7109375" customWidth="1"/>
+    <col min="23" max="23" width="55.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:23">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -813,28 +826,31 @@
       <c r="V1" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="2" spans="1:22">
+      <c r="W1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H2">
         <v>56</v>
@@ -858,36 +874,39 @@
         <v>0</v>
       </c>
       <c r="T2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="U2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="V2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22">
+        <v>55</v>
+      </c>
+      <c r="W2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H3">
         <v>25</v>
@@ -911,36 +930,39 @@
         <v>5</v>
       </c>
       <c r="T3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="U3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="V3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22">
+        <v>55</v>
+      </c>
+      <c r="W3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H4">
         <v>17</v>
@@ -964,36 +986,39 @@
         <v>7</v>
       </c>
       <c r="T4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="U4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="V4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22">
+        <v>55</v>
+      </c>
+      <c r="W4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H5">
         <v>34</v>
@@ -1014,36 +1039,39 @@
         <v>-0.4779999999999999</v>
       </c>
       <c r="T5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="U5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="V5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22">
+        <v>55</v>
+      </c>
+      <c r="W5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H6">
         <v>56</v>
@@ -1067,36 +1095,39 @@
         <v>0</v>
       </c>
       <c r="T6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="U6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="V6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22">
+        <v>55</v>
+      </c>
+      <c r="W6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H7">
         <v>25</v>
@@ -1120,36 +1151,39 @@
         <v>5</v>
       </c>
       <c r="T7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="U7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="V7" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22">
+        <v>55</v>
+      </c>
+      <c r="W7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H8">
         <v>17</v>
@@ -1173,36 +1207,39 @@
         <v>7</v>
       </c>
       <c r="T8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="U8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="V8" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22">
+        <v>55</v>
+      </c>
+      <c r="W8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H9">
         <v>34</v>
@@ -1223,36 +1260,39 @@
         <v>-0.5</v>
       </c>
       <c r="T9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="U9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="V9" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22">
+        <v>55</v>
+      </c>
+      <c r="W9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H10">
         <v>56</v>
@@ -1276,36 +1316,39 @@
         <v>0</v>
       </c>
       <c r="T10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="U10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="V10" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22">
+        <v>55</v>
+      </c>
+      <c r="W10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H11">
         <v>25</v>
@@ -1329,36 +1372,39 @@
         <v>5</v>
       </c>
       <c r="T11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="U11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="V11" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22">
+        <v>55</v>
+      </c>
+      <c r="W11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H12">
         <v>17</v>
@@ -1382,36 +1428,39 @@
         <v>7</v>
       </c>
       <c r="T12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="U12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="V12" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22">
+        <v>55</v>
+      </c>
+      <c r="W12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H13">
         <v>34</v>
@@ -1432,13 +1481,16 @@
         <v>-0.498</v>
       </c>
       <c r="T13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="U13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="V13" t="s">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="W13" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
